--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484817_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484817_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.565</v>
+        <v>4.9413</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7802</v>
+        <v>3.5798</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7848</v>
+        <v>1.3615</v>
       </c>
       <c r="G2" t="n">
         <v>2.3092</v>
@@ -610,13 +610,13 @@
         <v>2.6418</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3098</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7737000000000001</v>
+        <v>0.0259</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4639</v>
+        <v>0.0407</v>
       </c>
       <c r="V2" t="n">
         <v>2.7543</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5536</v>
+        <v>1.9358</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2539</v>
+        <v>-0.1363</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8075</v>
+        <v>2.072</v>
       </c>
       <c r="G3" t="n">
         <v>1.7132</v>
@@ -688,13 +688,13 @@
         <v>1.1322</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6125</v>
+        <v>-0.2304</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6808</v>
+        <v>-0.5632</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0682</v>
+        <v>0.3328</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3018</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FERRAGUT SEBASTIA</t>
+          <t>D. SARRIAS SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6049</v>
+        <v>0.9042</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7147</v>
+        <v>0.6929</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3196</v>
+        <v>0.2113</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.4577</v>
+        <v>-0.3153</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5893</v>
+        <v>-2.1772</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8684</v>
+        <v>1.8619</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0569</v>
+        <v>1.3104</v>
       </c>
       <c r="K5" t="n">
-        <v>1.184</v>
+        <v>-1.3304</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.241</v>
+        <v>2.6408</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4008</v>
+        <v>-1.6257</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7733</v>
+        <v>-0.8467</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.7789</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.4531</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0192</v>
+        <v>-0.1887</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0192</v>
+        <v>2.6418</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5343</v>
+        <v>0.0116</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1162</v>
+        <v>-0.4288</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5819</v>
+        <v>0.4404</v>
       </c>
       <c r="V5" t="n">
-        <v>2.5284</v>
+        <v>-1.2452</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.2832</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4977</v>
+        <v>0.577</v>
       </c>
       <c r="E6" t="n">
         <v>0.5962</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.0192</v>
       </c>
       <c r="G6" t="n">
         <v>0.6335</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1358</v>
+        <v>-0.0564</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0588</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.077</v>
+        <v>0.0024</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. RIVAS OSETE</t>
+          <t>A. FERRAGUT SEBASTIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1878</v>
+        <v>0.1076</v>
       </c>
       <c r="E7" t="n">
-        <v>0.633</v>
+        <v>-1.3178</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4452</v>
+        <v>1.4255</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2019</v>
+        <v>-2.4577</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3318</v>
+        <v>-0.5893</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1299</v>
+        <v>-1.8684</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0423</v>
+        <v>-0.0569</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0423</v>
+        <v>1.184</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.241</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2442</v>
+        <v>-2.4008</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3741</v>
+        <v>-1.7733</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1299</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.0192</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1887</v>
+        <v>3.0192</v>
       </c>
       <c r="S7" t="n">
-        <v>0.201</v>
+        <v>0.037</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5908</v>
+        <v>0.5131</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3897</v>
+        <v>-0.4761</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.5284</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.2832</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SARRIAS SANCHEZ</t>
+          <t>H. RIVAS OSETE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1084</v>
+        <v>-0.1045</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0294</v>
+        <v>0.3407</v>
       </c>
       <c r="F8" t="n">
-        <v>0.079</v>
+        <v>-0.4452</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3153</v>
+        <v>-0.2019</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1772</v>
+        <v>-0.3318</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8619</v>
+        <v>0.1299</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3104</v>
+        <v>0.0423</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3304</v>
+        <v>0.0423</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6408</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6257</v>
+        <v>-0.2442</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8467</v>
+        <v>-0.3741</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7789</v>
+        <v>0.1299</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4531</v>
+        <v>0.1887</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6418</v>
+        <v>0.1887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7842</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0923</v>
+        <v>0.2985</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3081</v>
+        <v>-0.3897</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2746</v>
+        <v>-0.3158</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6119</v>
+        <v>-2.4943</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3372</v>
+        <v>2.1785</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8401999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0417</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5168</v>
+        <v>-0.3992</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5162</v>
+        <v>0.3574</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3588</v>
+        <v>-1.2426</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4735</v>
+        <v>0.2987</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8323</v>
+        <v>-1.5413</v>
       </c>
       <c r="G10" t="n">
         <v>-2.113</v>
@@ -1234,13 +1234,13 @@
         <v>2.2644</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.227</v>
+        <v>-0.1107</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6895</v>
+        <v>0.5147</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9164</v>
+        <v>-0.6254</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3398</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2358</v>
+        <v>-3.2241</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9981</v>
+        <v>-2.8805</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2378</v>
+        <v>-0.3436</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0942</v>
@@ -1312,13 +1312,13 @@
         <v>0.5661</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1417</v>
+        <v>-0.1299</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3992</v>
+        <v>-0.2816</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2575</v>
+        <v>0.1517</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2452</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3409</v>
+        <v>-4.175</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7511</v>
+        <v>-2.4</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5899</v>
+        <v>-1.7751</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0087</v>
@@ -1390,13 +1390,13 @@
         <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2193</v>
+        <v>-0.0533</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5168</v>
+        <v>-0.1657</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2975</v>
+        <v>0.1123</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8678</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.2044</v>
+        <v>-5.1255</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3139</v>
+        <v>-4.235</v>
       </c>
       <c r="F13" t="n">
         <v>-0.8905</v>
@@ -1468,10 +1468,10 @@
         <v>0.9435</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5196</v>
+        <v>0.5986</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2627</v>
+        <v>0.3417</v>
       </c>
       <c r="U13" t="n">
         <v>0.2569</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.6632</v>
+        <v>-4.487699999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.8974</v>
+        <v>-6.7217</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2338</v>
+        <v>2.2339</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.4121</v>
+        <v>-5.412100000000001</v>
       </c>
       <c r="H14" t="n">
         <v>1.9487</v>
@@ -1525,7 +1525,7 @@
         <v>9.273599999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.657399999999999</v>
+        <v>-4.657400000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-10.0284</v>
@@ -1546,13 +1546,13 @@
         <v>16.0395</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.176</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3792</v>
+        <v>-0.2034</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2033000000000001</v>
+        <v>0.2034000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9622999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0971</v>
+        <v>3.9552</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7681</v>
+        <v>4.1835</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.671</v>
+        <v>-0.2283</v>
       </c>
       <c r="G15" t="n">
         <v>2.448</v>
@@ -1624,13 +1624,13 @@
         <v>2.0757</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7436</v>
+        <v>0.6017</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0081</v>
+        <v>0.4235</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2645</v>
+        <v>0.1782</v>
       </c>
       <c r="V15" t="n">
         <v>-0.038</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W. LADSON BUGALLO</t>
+          <t>M. VARELA BARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3555</v>
+        <v>2.5406</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3939</v>
+        <v>1.2809</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0383</v>
+        <v>1.2596</v>
       </c>
       <c r="G16" t="n">
-        <v>0.614</v>
+        <v>5.5808</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1354</v>
+        <v>-0.2943</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7494</v>
+        <v>5.8751</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3955</v>
+        <v>6.5795</v>
       </c>
       <c r="K16" t="n">
-        <v>1.231</v>
+        <v>1.5276</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1645</v>
+        <v>5.0519</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7815</v>
+        <v>-0.9987</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3664</v>
+        <v>-1.8219</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5849</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9435</v>
+        <v>-3.774</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1322</v>
+        <v>-6.0384</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0757</v>
+        <v>2.2644</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8436</v>
+        <v>0.413</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1147</v>
+        <v>0.1172</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7289</v>
+        <v>0.2958</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.3208</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2452</v>
+        <v>0.6226</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6036</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. VARELA BARCIA</t>
+          <t>W. LADSON BUGALLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1718</v>
+        <v>2.2757</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6963</v>
+        <v>1.6862</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4754</v>
+        <v>0.5895</v>
       </c>
       <c r="G17" t="n">
-        <v>5.5808</v>
+        <v>0.614</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2943</v>
+        <v>-0.1354</v>
       </c>
       <c r="I17" t="n">
-        <v>5.8751</v>
+        <v>0.7494</v>
       </c>
       <c r="J17" t="n">
-        <v>6.5795</v>
+        <v>1.3955</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5276</v>
+        <v>1.231</v>
       </c>
       <c r="L17" t="n">
-        <v>5.0519</v>
+        <v>0.1645</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9987</v>
+        <v>-0.7815</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8219</v>
+        <v>-1.3664</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.5849</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.774</v>
+        <v>0.9435</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6.0384</v>
+        <v>-1.1322</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2644</v>
+        <v>2.0757</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9558</v>
+        <v>0.0766</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4674</v>
+        <v>0.1776</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4884</v>
+        <v>-0.1011</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3208</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6226</v>
+        <v>1.2452</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3018</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. CAMARA</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1453</v>
+        <v>1.388</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9801</v>
+        <v>1.3964</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8347</v>
+        <v>-0.0083</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2424</v>
+        <v>-0.2535</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9266</v>
+        <v>0.4437</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6842</v>
+        <v>-0.6972</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6833</v>
+        <v>0.8364</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6747</v>
+        <v>1.4689</v>
       </c>
       <c r="L18" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.6325</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4408</v>
+        <v>-1.0899</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7482</v>
+        <v>-1.0252</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6927</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="P18" t="n">
         <v>0.7548</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7548</v>
+        <v>1.6983</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1481</v>
+        <v>0.2451</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2968</v>
+        <v>-0.0436</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1487</v>
+        <v>0.2887</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GOMEZ-ARRONES MORGADO</t>
+          <t>O. CAMARA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8199</v>
+        <v>1.001</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0652</v>
+        <v>1.7852</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8851</v>
+        <v>-0.7842</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1321</v>
+        <v>0.2424</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0172</v>
+        <v>0.9266</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1149</v>
+        <v>-0.6842</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1688</v>
+        <v>1.6833</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4226</v>
+        <v>1.6747</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5914</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0367</v>
+        <v>-1.4408</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4398</v>
+        <v>-0.7482</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4765</v>
+        <v>-0.6927</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9435</v>
+        <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4991</v>
+        <v>0.0038</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7642</v>
+        <v>0.102</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2634</v>
+        <v>-0.0982</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>A. GOMEZ-ARRONES MORGADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2165</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6169</v>
+        <v>-1.7729</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4004</v>
+        <v>2.7241</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2535</v>
+        <v>-0.1321</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4437</v>
+        <v>-0.0172</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6972</v>
+        <v>-0.1149</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8364</v>
+        <v>-0.1688</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4689</v>
+        <v>0.4226</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6325</v>
+        <v>-0.5914</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0899</v>
+        <v>0.0367</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0252</v>
+        <v>-0.4398</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.4765</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7548</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6983</v>
+        <v>0.9435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9264</v>
+        <v>0.6303</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.823</v>
+        <v>-0.4719</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1034</v>
+        <v>1.1023</v>
       </c>
       <c r="V20" t="n">
         <v>0.6415999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9054</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.3774</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.1901</v>
+        <v>-2.4244</v>
       </c>
       <c r="F21" t="n">
-        <v>4.1103</v>
+        <v>2.047</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2794</v>
+        <v>-0.0267</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1177</v>
+        <v>-0.295</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8383</v>
+        <v>0.2683</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8784</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0925</v>
+        <v>0.486</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2142</v>
+        <v>-1.1176</v>
       </c>
       <c r="M21" t="n">
-        <v>0.599</v>
+        <v>0.6049</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0252</v>
+        <v>-0.781</v>
       </c>
       <c r="O21" t="n">
-        <v>1.6242</v>
+        <v>1.3859</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0757</v>
+        <v>0.1887</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.1514</v>
+        <v>-1.3209</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0757</v>
+        <v>1.5096</v>
       </c>
       <c r="S21" t="n">
-        <v>2.9169</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>1.4813</v>
+        <v>-0.4719</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4357</v>
+        <v>0.5362</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.6036</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2848</v>
+        <v>-0.4207</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.204</v>
+        <v>-1.4963</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9193</v>
+        <v>1.0756</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1407</v>
@@ -2170,13 +2170,13 @@
         <v>0.5661</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4785</v>
+        <v>0.3426</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1793</v>
+        <v>-0.113</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2992</v>
+        <v>0.4556</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1676</v>
+        <v>-1.4676</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7167</v>
+        <v>-5.3593</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5491</v>
+        <v>3.8916</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0267</v>
+        <v>-0.2794</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.295</v>
+        <v>-2.1177</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2683</v>
+        <v>1.8383</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.8784</v>
       </c>
       <c r="K23" t="n">
-        <v>0.486</v>
+        <v>-1.0925</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1176</v>
+        <v>0.2142</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6049</v>
+        <v>0.599</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.781</v>
+        <v>-1.0252</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3859</v>
+        <v>1.6242</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1887</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3209</v>
+        <v>-4.1514</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5096</v>
+        <v>2.0757</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.726</v>
+        <v>1.529</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7642</v>
+        <v>0.3121</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0383</v>
+        <v>1.2169</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6036</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.6108</v>
+        <v>-1.5843</v>
       </c>
       <c r="E24" t="n">
         <v>-1.5131</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0977</v>
+        <v>-0.0712</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6408</v>
@@ -2326,13 +2326,13 @@
         <v>0.1887</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1587</v>
+        <v>-0.1323</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2352</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0764</v>
+        <v>0.1029</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.663200000000001</v>
+        <v>8.2616</v>
       </c>
       <c r="E25" t="n">
         <v>-2.2338</v>
       </c>
       <c r="F25" t="n">
-        <v>7.8971</v>
+        <v>10.4954</v>
       </c>
       <c r="G25" t="n">
-        <v>5.411999999999999</v>
+        <v>5.412000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>-1.9487</v>
@@ -2380,7 +2380,7 @@
         <v>10.0283</v>
       </c>
       <c r="K25" t="n">
-        <v>7.3249</v>
+        <v>7.324900000000001</v>
       </c>
       <c r="L25" t="n">
         <v>2.7033</v>
@@ -2395,7 +2395,7 @@
         <v>4.657400000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.887</v>
+        <v>-1.886999999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-16.0395</v>
@@ -2404,22 +2404,22 @@
         <v>14.1525</v>
       </c>
       <c r="S25" t="n">
-        <v>1.1757</v>
+        <v>3.774</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2031999999999999</v>
+        <v>-0.2032</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3791</v>
+        <v>3.9773</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9623999999999998</v>
+        <v>0.9623999999999997</v>
       </c>
       <c r="W25" t="n">
         <v>3.9804</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.018000000000001</v>
+        <v>-3.018</v>
       </c>
     </row>
   </sheetData>
